--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -31,9 +31,6 @@
     <x:t>candidate_party_affiliation</x:t>
   </x:si>
   <x:si>
-    <x:t>candidate_election_year</x:t>
-  </x:si>
-  <x:si>
     <x:t>candidate_office</x:t>
   </x:si>
   <x:si>
@@ -91,6 +88,21 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
+    <x:t>H6IL09228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00905307</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00799031</x:t>
   </x:si>
   <x:si>
@@ -115,9 +127,6 @@
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00904326</x:t>
   </x:si>
   <x:si>
@@ -134,9 +143,6 @@
   </x:si>
   <x:si>
     <x:t>C00656686</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
   </x:si>
   <x:si>
     <x:t>C00935049</x:t>
@@ -239,23 +245,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:N7" totalsRowShown="0">
-  <x:autoFilter ref="A1:N7"/>
-  <x:tableColumns count="14">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M32" totalsRowShown="0">
+  <x:autoFilter ref="A1:M32"/>
+  <x:tableColumns count="13">
     <x:tableColumn id="1" name="committee_id"/>
     <x:tableColumn id="2" name="committee_name"/>
     <x:tableColumn id="3" name="candidate_id"/>
     <x:tableColumn id="4" name="candidate_name"/>
     <x:tableColumn id="5" name="candidate_party_affiliation"/>
-    <x:tableColumn id="6" name="candidate_election_year"/>
-    <x:tableColumn id="7" name="candidate_office"/>
-    <x:tableColumn id="8" name="candidate_office_district"/>
-    <x:tableColumn id="9" name="candidate_office_state"/>
-    <x:tableColumn id="10" name="candidate_incumbent_challenger_status"/>
-    <x:tableColumn id="11" name="candidate_principal_campaign_committee"/>
-    <x:tableColumn id="12" name="expenditure"/>
-    <x:tableColumn id="13" name="election_cycle"/>
-    <x:tableColumn id="14" name="expenditure_description"/>
+    <x:tableColumn id="6" name="candidate_office"/>
+    <x:tableColumn id="7" name="candidate_office_district"/>
+    <x:tableColumn id="8" name="candidate_office_state"/>
+    <x:tableColumn id="9" name="candidate_incumbent_challenger_status"/>
+    <x:tableColumn id="10" name="candidate_principal_campaign_committee"/>
+    <x:tableColumn id="11" name="expenditure"/>
+    <x:tableColumn id="12" name="election_cycle"/>
+    <x:tableColumn id="13" name="expenditure_description"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -549,7 +554,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:N7"/>
+  <x:dimension ref="A1:M32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15.710625" style="0" customWidth="1"/>
@@ -557,18 +562,17 @@
     <x:col min="3" max="3" width="14.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="25.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="27.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="25.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17.853482" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="25.282054" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="39.996339" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="41.567768" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13.853482" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="15.710625" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="25.282054" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.853482" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25.282054" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.424911" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="39.996339" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="41.567768" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15.710625" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="25.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:14">
+    <x:row r="1" spans="1:13">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -608,28 +612,25 @@
       <x:c r="M1" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N1" s="0" t="s">
+    </x:row>
+    <x:row r="2" spans="1:13">
+      <x:c r="A2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:14">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="B2" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="C2" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="D2" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F2" s="0">
-        <x:v>2026</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
         <x:v>19</x:v>
@@ -643,43 +644,40 @@
       <x:c r="J2" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="K2" s="0">
+        <x:v>251132</x:v>
       </x:c>
       <x:c r="L2" s="0">
-        <x:v>2029950</x:v>
-      </x:c>
-      <x:c r="M2" s="0">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:14">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:13">
       <x:c r="A3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>2026</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>21</x:v>
@@ -687,43 +685,40 @@
       <x:c r="J3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="K3" s="0">
+        <x:v>100537</x:v>
       </x:c>
       <x:c r="L3" s="0">
-        <x:v>1443368</x:v>
-      </x:c>
-      <x:c r="M3" s="0">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:14">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:13">
       <x:c r="A4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="C4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>2026</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>21</x:v>
@@ -731,87 +726,81 @@
       <x:c r="J4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>34</x:v>
+      <x:c r="K4" s="0">
+        <x:v>2250042</x:v>
       </x:c>
       <x:c r="L4" s="0">
-        <x:v>1959944</x:v>
-      </x:c>
-      <x:c r="M4" s="0">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:14">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:13">
       <x:c r="A5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>2022</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K5" s="0">
+        <x:v>252071</x:v>
       </x:c>
       <x:c r="L5" s="0">
-        <x:v>2326917</x:v>
-      </x:c>
-      <x:c r="M5" s="0">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:14">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:13">
       <x:c r="A6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>2026</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>21</x:v>
@@ -819,61 +808,1080 @@
       <x:c r="J6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K6" s="0" t="s">
+      <x:c r="K6" s="0">
+        <x:v>40000</x:v>
+      </x:c>
+      <x:c r="L6" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:13">
+      <x:c r="A7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K7" s="0">
+        <x:v>94439</x:v>
+      </x:c>
+      <x:c r="L7" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:13">
+      <x:c r="A8" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K8" s="0">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="L8" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:13">
+      <x:c r="A9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K9" s="0">
+        <x:v>128800</x:v>
+      </x:c>
+      <x:c r="L9" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:13">
+      <x:c r="A10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K10" s="0">
+        <x:v>75000</x:v>
+      </x:c>
+      <x:c r="L10" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:13">
+      <x:c r="A11" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K11" s="0">
+        <x:v>16500</x:v>
+      </x:c>
+      <x:c r="L11" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:13">
+      <x:c r="A12" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K12" s="0">
+        <x:v>286800</x:v>
+      </x:c>
+      <x:c r="L12" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:13">
+      <x:c r="A13" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K13" s="0">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="L13" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:13">
+      <x:c r="A14" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K14" s="0">
+        <x:v>185715</x:v>
+      </x:c>
+      <x:c r="L14" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:13">
+      <x:c r="A15" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K15" s="0">
+        <x:v>1750000</x:v>
+      </x:c>
+      <x:c r="L15" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:13">
+      <x:c r="A16" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K16" s="0">
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="L16" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:13">
+      <x:c r="A17" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K17" s="0">
+        <x:v>39000</x:v>
+      </x:c>
+      <x:c r="L17" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:13">
+      <x:c r="A18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K18" s="0">
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="L18" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:13">
+      <x:c r="A19" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K19" s="0">
+        <x:v>326686</x:v>
+      </x:c>
+      <x:c r="L19" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:13">
+      <x:c r="A20" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K20" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="L20" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:13">
+      <x:c r="A21" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K21" s="0">
+        <x:v>1453343</x:v>
+      </x:c>
+      <x:c r="L21" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M21" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:13">
+      <x:c r="A22" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K22" s="0">
+        <x:v>75000</x:v>
+      </x:c>
+      <x:c r="L22" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M22" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:13">
+      <x:c r="A23" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K23" s="0">
+        <x:v>347944</x:v>
+      </x:c>
+      <x:c r="L23" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:13">
+      <x:c r="A24" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K24" s="0">
+        <x:v>450630</x:v>
+      </x:c>
+      <x:c r="L24" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M24" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:13">
+      <x:c r="A25" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L6" s="0">
-        <x:v>1494864</x:v>
-      </x:c>
-      <x:c r="M6" s="0">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:14">
-      <x:c r="A7" s="0" t="s">
+      <x:c r="E25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="H25" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="K25" s="0">
+        <x:v>1900000</x:v>
+      </x:c>
+      <x:c r="L25" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M25" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:13">
+      <x:c r="A26" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K26" s="0">
+        <x:v>149745</x:v>
+      </x:c>
+      <x:c r="L26" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M26" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:13">
+      <x:c r="A27" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K27" s="0">
+        <x:v>225000</x:v>
+      </x:c>
+      <x:c r="L27" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M27" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:13">
+      <x:c r="A28" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K28" s="0">
+        <x:v>32250</x:v>
+      </x:c>
+      <x:c r="L28" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:13">
+      <x:c r="A29" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K29" s="0">
+        <x:v>52448</x:v>
+      </x:c>
+      <x:c r="L29" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M29" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:13">
+      <x:c r="A30" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="B30" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F7" s="0">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
+      <x:c r="C30" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
+      <x:c r="D30" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K7" s="0" t="s">
+      <x:c r="E30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="L7" s="0">
-        <x:v>38952</x:v>
-      </x:c>
-      <x:c r="M7" s="0">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="H30" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K30" s="0">
+        <x:v>2780</x:v>
+      </x:c>
+      <x:c r="L30" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M30" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:13">
+      <x:c r="A31" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K31" s="0">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="L31" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M31" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:13">
+      <x:c r="A32" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K32" s="0">
+        <x:v>27172</x:v>
+      </x:c>
+      <x:c r="L32" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M32" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -101,6 +101,12 @@
   </x:si>
   <x:si>
     <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
   </x:si>
   <x:si>
     <x:t>C00799031</x:t>
@@ -245,8 +251,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M32" totalsRowShown="0">
-  <x:autoFilter ref="A1:M32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M34" totalsRowShown="0">
+  <x:autoFilter ref="A1:M34"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="committee_id"/>
     <x:tableColumn id="2" name="committee_name"/>
@@ -554,7 +560,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M32"/>
+  <x:dimension ref="A1:M34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15.710625" style="0" customWidth="1"/>
@@ -645,7 +651,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K2" s="0">
-        <x:v>251132</x:v>
+        <x:v>100537</x:v>
       </x:c>
       <x:c r="L2" s="0">
         <x:v>2026</x:v>
@@ -686,7 +692,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K3" s="0">
-        <x:v>100537</x:v>
+        <x:v>2650042</x:v>
       </x:c>
       <x:c r="L3" s="0">
         <x:v>2026</x:v>
@@ -727,7 +733,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K4" s="0">
-        <x:v>2250042</x:v>
+        <x:v>294083</x:v>
       </x:c>
       <x:c r="L4" s="0">
         <x:v>2026</x:v>
@@ -768,7 +774,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K5" s="0">
-        <x:v>252071</x:v>
+        <x:v>350566</x:v>
       </x:c>
       <x:c r="L5" s="0">
         <x:v>2026</x:v>
@@ -850,7 +856,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K7" s="0">
-        <x:v>94439</x:v>
+        <x:v>153800</x:v>
       </x:c>
       <x:c r="L7" s="0">
         <x:v>2026</x:v>
@@ -891,7 +897,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K8" s="0">
-        <x:v>500000</x:v>
+        <x:v>16625</x:v>
       </x:c>
       <x:c r="L8" s="0">
         <x:v>2026</x:v>
@@ -932,7 +938,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K9" s="0">
-        <x:v>128800</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="L9" s="0">
         <x:v>2026</x:v>
@@ -973,7 +979,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K10" s="0">
-        <x:v>75000</x:v>
+        <x:v>180954</x:v>
       </x:c>
       <x:c r="L10" s="0">
         <x:v>2026</x:v>
@@ -1014,7 +1020,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K11" s="0">
-        <x:v>16500</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="L11" s="0">
         <x:v>2026</x:v>
@@ -1031,10 +1037,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>17</x:v>
@@ -1043,7 +1049,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>20</x:v>
@@ -1052,10 +1058,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K12" s="0">
-        <x:v>286800</x:v>
+        <x:v>6750</x:v>
       </x:c>
       <x:c r="L12" s="0">
         <x:v>2026</x:v>
@@ -1072,10 +1078,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>17</x:v>
@@ -1084,7 +1090,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
         <x:v>20</x:v>
@@ -1093,10 +1099,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K13" s="0">
-        <x:v>100000</x:v>
+        <x:v>91163</x:v>
       </x:c>
       <x:c r="L13" s="0">
         <x:v>2026</x:v>
@@ -1107,16 +1113,16 @@
     </x:row>
     <x:row r="14" spans="1:13">
       <x:c r="A14" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>17</x:v>
@@ -1125,7 +1131,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>20</x:v>
@@ -1134,10 +1140,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K14" s="0">
-        <x:v>185715</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="L14" s="0">
         <x:v>2026</x:v>
@@ -1148,16 +1154,16 @@
     </x:row>
     <x:row r="15" spans="1:13">
       <x:c r="A15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>17</x:v>
@@ -1166,7 +1172,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>20</x:v>
@@ -1175,10 +1181,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K15" s="0">
-        <x:v>1750000</x:v>
+        <x:v>185715</x:v>
       </x:c>
       <x:c r="L15" s="0">
         <x:v>2026</x:v>
@@ -1189,37 +1195,37 @@
     </x:row>
     <x:row r="16" spans="1:13">
       <x:c r="A16" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D16" s="0" t="s">
+      <x:c r="H16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I16" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="K16" s="0">
-        <x:v>80000</x:v>
+        <x:v>376800</x:v>
       </x:c>
       <x:c r="L16" s="0">
         <x:v>2026</x:v>
@@ -1230,37 +1236,37 @@
     </x:row>
     <x:row r="17" spans="1:13">
       <x:c r="A17" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D17" s="0" t="s">
+      <x:c r="H17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="K17" s="0">
-        <x:v>39000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="L17" s="0">
         <x:v>2026</x:v>
@@ -1277,10 +1283,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>17</x:v>
@@ -1298,10 +1304,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K18" s="0">
-        <x:v>400000</x:v>
+        <x:v>39125</x:v>
       </x:c>
       <x:c r="L18" s="0">
         <x:v>2026</x:v>
@@ -1318,10 +1324,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>17</x:v>
@@ -1339,10 +1345,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K19" s="0">
-        <x:v>326686</x:v>
+        <x:v>80000</x:v>
       </x:c>
       <x:c r="L19" s="0">
         <x:v>2026</x:v>
@@ -1359,10 +1365,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
         <x:v>17</x:v>
@@ -1380,10 +1386,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K20" s="0">
-        <x:v>2000000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="L20" s="0">
         <x:v>2026</x:v>
@@ -1394,98 +1400,98 @@
     </x:row>
     <x:row r="21" spans="1:13">
       <x:c r="A21" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D21" s="0" t="s">
+      <x:c r="E21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H21" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="K21" s="0">
-        <x:v>1453343</x:v>
+        <x:v>425575</x:v>
       </x:c>
       <x:c r="L21" s="0">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:13">
       <x:c r="A22" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D22" s="0" t="s">
+      <x:c r="E22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H22" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I22" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="K22" s="0">
-        <x:v>75000</x:v>
+        <x:v>2700000</x:v>
       </x:c>
       <x:c r="L22" s="0">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:13">
       <x:c r="A23" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
         <x:v>17</x:v>
@@ -1494,19 +1500,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K23" s="0">
-        <x:v>347944</x:v>
+        <x:v>450630</x:v>
       </x:c>
       <x:c r="L23" s="0">
         <x:v>2026</x:v>
@@ -1517,16 +1523,16 @@
     </x:row>
     <x:row r="24" spans="1:13">
       <x:c r="A24" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
         <x:v>17</x:v>
@@ -1535,19 +1541,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K24" s="0">
-        <x:v>450630</x:v>
+        <x:v>347944</x:v>
       </x:c>
       <x:c r="L24" s="0">
         <x:v>2026</x:v>
@@ -1558,98 +1564,98 @@
     </x:row>
     <x:row r="25" spans="1:13">
       <x:c r="A25" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
+      <x:c r="J25" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I25" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="K25" s="0">
-        <x:v>1900000</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="L25" s="0">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="M25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:13">
       <x:c r="A26" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
+      <x:c r="J26" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I26" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="K26" s="0">
-        <x:v>149745</x:v>
+        <x:v>1453343</x:v>
       </x:c>
       <x:c r="L26" s="0">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="M26" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:13">
       <x:c r="A27" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
         <x:v>17</x:v>
@@ -1658,7 +1664,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
         <x:v>20</x:v>
@@ -1667,10 +1673,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K27" s="0">
-        <x:v>225000</x:v>
+        <x:v>2600000</x:v>
       </x:c>
       <x:c r="L27" s="0">
         <x:v>2026</x:v>
@@ -1681,16 +1687,16 @@
     </x:row>
     <x:row r="28" spans="1:13">
       <x:c r="A28" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
         <x:v>17</x:v>
@@ -1699,7 +1705,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
         <x:v>20</x:v>
@@ -1708,10 +1714,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K28" s="0">
-        <x:v>32250</x:v>
+        <x:v>325000</x:v>
       </x:c>
       <x:c r="L28" s="0">
         <x:v>2026</x:v>
@@ -1722,16 +1728,16 @@
     </x:row>
     <x:row r="29" spans="1:13">
       <x:c r="A29" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
         <x:v>17</x:v>
@@ -1740,7 +1746,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
         <x:v>20</x:v>
@@ -1749,10 +1755,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K29" s="0">
-        <x:v>52448</x:v>
+        <x:v>149745</x:v>
       </x:c>
       <x:c r="L29" s="0">
         <x:v>2026</x:v>
@@ -1763,37 +1769,37 @@
     </x:row>
     <x:row r="30" spans="1:13">
       <x:c r="A30" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B30" s="0" t="s">
+      <x:c r="H30" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G30" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H30" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I30" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="K30" s="0">
-        <x:v>2780</x:v>
+        <x:v>32250</x:v>
       </x:c>
       <x:c r="L30" s="0">
         <x:v>2026</x:v>
@@ -1804,37 +1810,37 @@
     </x:row>
     <x:row r="31" spans="1:13">
       <x:c r="A31" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B31" s="0" t="s">
+      <x:c r="H31" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G31" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H31" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I31" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J31" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="K31" s="0">
-        <x:v>9000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="L31" s="0">
         <x:v>2026</x:v>
@@ -1845,42 +1851,124 @@
     </x:row>
     <x:row r="32" spans="1:13">
       <x:c r="A32" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K32" s="0">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="L32" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M32" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:13">
+      <x:c r="A33" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D32" s="0" t="s">
+      <x:c r="B33" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F32" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
+      <x:c r="C33" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H32" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I32" s="0" t="s">
+      <x:c r="D33" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J32" s="0" t="s">
+      <x:c r="E33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K32" s="0">
+      <x:c r="H33" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K33" s="0">
+        <x:v>2780</x:v>
+      </x:c>
+      <x:c r="L33" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M33" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:13">
+      <x:c r="A34" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K34" s="0">
         <x:v>27172</x:v>
       </x:c>
-      <x:c r="L32" s="0">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="M32" s="0" t="s">
+      <x:c r="L34" s="0">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M34" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -121,12 +121,36 @@
     <x:t>07</x:t>
   </x:si>
   <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2NC06114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL07339</x:t>
   </x:si>
   <x:si>
@@ -157,19 +181,19 @@
     <x:t>02</x:t>
   </x:si>
   <x:si>
+    <x:t>H6NJ11310</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00710848</x:t>
   </x:si>
   <x:si>
     <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NJ11310</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -240,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J12" totalsRowShown="0">
-  <x:autoFilter ref="A1:J12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
+  <x:autoFilter ref="A1:J15"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -546,7 +570,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J12"/>
+  <x:dimension ref="A1:J15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -788,16 +812,16 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>14</x:v>
@@ -809,7 +833,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>4383749</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -820,10 +844,10 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>37</x:v>
@@ -835,114 +859,210 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>59748</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>2326917</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>4379246</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="H12" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="I12" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:10">
+      <x:c r="A13" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
+      <x:c r="B13" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H12" s="1">
+      <x:c r="C13" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H13" s="1">
+        <x:v>4379246</x:v>
+      </x:c>
+      <x:c r="I13" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
+      <x:c r="A14" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H14" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I14" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
+      <x:c r="A15" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
         <x:v>38952</x:v>
       </x:c>
-      <x:c r="I12" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J12" s="1" t="s">
+      <x:c r="I15" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -79,6 +79,15 @@
     <x:t>08</x:t>
   </x:si>
   <x:si>
+    <x:t>H6IL09236</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00936724</x:t>
   </x:si>
   <x:si>
@@ -89,9 +98,6 @@
   </x:si>
   <x:si>
     <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
     <x:t>H6IL09228</x:t>
@@ -264,8 +270,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
-  <x:autoFilter ref="A1:J15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
+  <x:autoFilter ref="A1:J16"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -570,7 +576,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J15"/>
+  <x:dimension ref="A1:J16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -673,7 +679,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>163879</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -684,42 +690,42 @@
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>3985700</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>26</x:v>
@@ -731,33 +737,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>1426379</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
@@ -769,13 +775,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>149773</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
@@ -786,74 +792,74 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>4968502</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>500346</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
@@ -865,85 +871,85 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>4383749</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>600000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="G11" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>59748</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>47</x:v>
@@ -955,13 +961,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>2326917</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -972,98 +978,130 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>350000</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I15" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H15" s="1">
+      <x:c r="D16" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H16" s="1">
         <x:v>38952</x:v>
       </x:c>
-      <x:c r="I15" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="s">
-        <x:v>25</x:v>
+      <x:c r="I16" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -187,6 +187,12 @@
     <x:t>02</x:t>
   </x:si>
   <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6NJ11310</x:t>
   </x:si>
   <x:si>
@@ -194,12 +200,6 @@
   </x:si>
   <x:si>
     <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -270,8 +270,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
-  <x:autoFilter ref="A1:J16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
+  <x:autoFilter ref="A1:J15"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -576,7 +576,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J16"/>
+  <x:dimension ref="A1:J15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1042,65 +1042,33 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>350000</x:v>
+        <x:v>15130</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:10">
-      <x:c r="A16" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H16" s="1">
-        <x:v>38952</x:v>
-      </x:c>
-      <x:c r="I16" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -127,36 +127,12 @@
     <x:t>07</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2NC06114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6IL07339</x:t>
   </x:si>
   <x:si>
@@ -185,21 +161,6 @@
   </x:si>
   <x:si>
     <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NJ11310</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -270,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
-  <x:autoFilter ref="A1:J15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J12" totalsRowShown="0">
+  <x:autoFilter ref="A1:J12"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -576,7 +537,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J15"/>
+  <x:dimension ref="A1:J12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -839,7 +800,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>4968502</x:v>
+        <x:v>2645986</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -850,16 +811,16 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
@@ -871,7 +832,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>500346</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -882,10 +843,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>39</x:v>
@@ -897,178 +858,82 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>4383749</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>600000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>59748</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:10">
-      <x:c r="A13" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H13" s="1">
-        <x:v>2326917</x:v>
-      </x:c>
-      <x:c r="I13" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:10">
-      <x:c r="A14" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H14" s="1">
-        <x:v>4379246</x:v>
-      </x:c>
-      <x:c r="I14" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:10">
-      <x:c r="A15" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H15" s="1">
-        <x:v>15130</x:v>
-      </x:c>
-      <x:c r="I15" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -110,6 +110,24 @@
   </x:si>
   <x:si>
     <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8CA50098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
   </x:si>
   <x:si>
     <x:t>C00799031</x:t>
@@ -231,8 +249,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J12" totalsRowShown="0">
-  <x:autoFilter ref="A1:J12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J13" totalsRowShown="0">
+  <x:autoFilter ref="A1:J13"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -537,7 +555,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J12"/>
+  <x:dimension ref="A1:J13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -797,42 +815,42 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>2645986</x:v>
+        <x:v>750000</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>4383749</x:v>
+        <x:v>2645986</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -843,60 +861,60 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>59748</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>2326917</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -907,33 +925,65 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H12" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="I12" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:10">
+      <x:c r="A13" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H12" s="1">
+      <x:c r="H13" s="1">
         <x:v>4379246</x:v>
       </x:c>
-      <x:c r="I12" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J12" s="1" t="s">
+      <x:c r="I13" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -130,6 +130,24 @@
     <x:t>CA</x:t>
   </x:si>
   <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NE02190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00799031</x:t>
   </x:si>
   <x:si>
@@ -178,7 +196,10 @@
     <x:t>MILLER, DONNA</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
+    <x:t>H6NE02174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -249,8 +270,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J13" totalsRowShown="0">
-  <x:autoFilter ref="A1:J13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
+  <x:autoFilter ref="A1:J15"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -555,7 +576,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J13"/>
+  <x:dimension ref="A1:J15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -847,42 +868,42 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>2645986</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>4383749</x:v>
+        <x:v>2645986</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -893,60 +914,60 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>59748</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>2326917</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -957,33 +978,97 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H13" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="I13" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
+      <x:c r="A14" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H13" s="1">
+      <x:c r="H14" s="1">
         <x:v>4379246</x:v>
       </x:c>
-      <x:c r="I13" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J13" s="1" t="s">
+      <x:c r="I14" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
+      <x:c r="A15" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="I15" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -175,6 +175,18 @@
     <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
+    <x:t>H6KY04171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
     <x:t>H8NJ07223</x:t>
   </x:si>
   <x:si>
@@ -182,6 +194,12 @@
   </x:si>
   <x:si>
     <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2KY04121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
   </x:si>
   <x:si>
     <x:t>C00935049</x:t>
@@ -270,8 +288,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
-  <x:autoFilter ref="A1:J15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
+  <x:autoFilter ref="A1:J17"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -576,7 +594,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J15"/>
+  <x:dimension ref="A1:J17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -993,59 +1011,59 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>2326917</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>60</x:v>
@@ -1057,18 +1075,82 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
+        <x:v>623905</x:v>
+      </x:c>
+      <x:c r="I15" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G15" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H16" s="1">
+        <x:v>4379246</x:v>
+      </x:c>
+      <x:c r="I16" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H15" s="1">
+      <x:c r="H17" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I15" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="s">
+      <x:c r="I17" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -148,49 +148,37 @@
     <x:t>NE</x:t>
   </x:si>
   <x:si>
+    <x:t>H6IL09194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00799031</x:t>
   </x:si>
   <x:si>
     <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
   </x:si>
   <x:si>
-    <x:t>H4IL07177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+    <x:t>H6KY04171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8NJ07223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
     <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL09194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL07339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6KY04171</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8NJ07223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
     <x:t>NJ</x:t>
@@ -288,8 +276,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
-  <x:autoFilter ref="A1:J17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
+  <x:autoFilter ref="A1:J15"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -594,7 +582,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J17"/>
+  <x:dimension ref="A1:J15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -900,28 +888,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>2645986</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -932,28 +920,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>4383749</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -964,28 +952,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>59748</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -996,161 +984,97 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>110101</x:v>
+        <x:v>623905</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>2326917</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>623905</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:10">
-      <x:c r="A16" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H16" s="1">
-        <x:v>4379246</x:v>
-      </x:c>
-      <x:c r="I16" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:10">
-      <x:c r="A17" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H17" s="1">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="I17" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -130,22 +130,22 @@
     <x:t>CA</x:t>
   </x:si>
   <x:si>
+    <x:t>H6NE02190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00863472</x:t>
   </x:si>
   <x:si>
     <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NE02190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
   </x:si>
   <x:si>
     <x:t>H6IL09194</x:t>
@@ -276,8 +276,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
-  <x:autoFilter ref="A1:J15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
+  <x:autoFilter ref="A1:J16"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -582,7 +582,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J15"/>
+  <x:dimension ref="A1:J16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -845,7 +845,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>750000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -856,28 +856,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="G9" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>150000</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -888,60 +888,60 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>4383749</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>110101</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -958,28 +958,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>2326917</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
@@ -990,22 +990,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>623905</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1016,65 +1016,97 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>4379246</x:v>
+        <x:v>623905</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
+        <x:v>4379246</x:v>
+      </x:c>
+      <x:c r="I15" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H15" s="1">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H16" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I15" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="s">
+      <x:c r="I16" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -909,7 +909,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>150000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1101,7 +1101,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>150000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -206,6 +206,18 @@
   </x:si>
   <x:si>
     <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8CA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -276,8 +288,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
-  <x:autoFilter ref="A1:J16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
+  <x:autoFilter ref="A1:J17"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -582,7 +594,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J16"/>
+  <x:dimension ref="A1:J17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -973,7 +985,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>110101</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1037,7 +1049,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>623905</x:v>
+        <x:v>1241841</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1107,6 +1119,38 @@
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H17" s="1">
+        <x:v>30801</x:v>
+      </x:c>
+      <x:c r="I17" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -985,7 +985,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>219149</x:v>
+        <x:v>221309</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>1241841</x:v>
+        <x:v>1250481</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1145,7 +1145,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>30801</x:v>
+        <x:v>86493</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -985,7 +985,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>221309</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>1250481</x:v>
+        <x:v>1830265</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -100,6 +100,24 @@
     <x:t>BEAN, MELISSA LUBURICH</x:t>
   </x:si>
   <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NJ07201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09228</x:t>
   </x:si>
   <x:si>
@@ -178,12 +196,6 @@
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>H2KY04121</x:t>
   </x:si>
   <x:si>
@@ -206,12 +218,6 @@
   </x:si>
   <x:si>
     <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
   </x:si>
   <x:si>
     <x:t>H8CA01109</x:t>
@@ -288,8 +294,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
-  <x:autoFilter ref="A1:J17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J18" totalsRowShown="0">
+  <x:autoFilter ref="A1:J18"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -594,7 +600,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J17"/>
+  <x:dimension ref="A1:J18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -772,48 +778,48 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>1426379</x:v>
+        <x:v>25305</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
@@ -825,21 +831,21 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>149773</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>34</x:v>
@@ -851,45 +857,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>1000000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1870</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -900,28 +906,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>198972</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -932,10 +938,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>44</x:v>
@@ -947,45 +953,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>4383749</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>374487</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -996,60 +1002,60 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>2326917</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>1830265</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1060,10 +1066,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>60</x:v>
@@ -1075,45 +1081,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1830265</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>198972</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1124,10 +1130,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>66</x:v>
@@ -1139,18 +1145,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>86493</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10">
+      <x:c r="A18" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H18" s="1">
+        <x:v>414981</x:v>
+      </x:c>
+      <x:c r="I18" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J18" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -224,6 +224,15 @@
   </x:si>
   <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6CA22190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -294,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J18" totalsRowShown="0">
-  <x:autoFilter ref="A1:J18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J19" totalsRowShown="0">
+  <x:autoFilter ref="A1:J19"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -600,7 +609,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J18"/>
+  <x:dimension ref="A1:J19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -895,7 +904,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1000000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1190,6 +1199,38 @@
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10">
+      <x:c r="A19" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H19" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I19" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J19" s="1" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -166,16 +166,40 @@
     <x:t>EDW ACTION FUND</x:t>
   </x:si>
   <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4IL07177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+    <x:t>H2NC06114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL07339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
     <x:t>H6KY04171</x:t>
@@ -184,9 +208,6 @@
     <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
     <x:t>KY</x:t>
   </x:si>
   <x:si>
@@ -233,6 +254,15 @@
   </x:si>
   <x:si>
     <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NJ11310</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -303,8 +333,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J19" totalsRowShown="0">
-  <x:autoFilter ref="A1:J19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
+  <x:autoFilter ref="A1:J25"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -609,7 +639,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J19"/>
+  <x:dimension ref="A1:J25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -808,7 +838,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>25305</x:v>
+        <x:v>50710</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -979,28 +1009,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>4383749</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1011,10 +1041,10 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>54</x:v>
@@ -1026,13 +1056,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>374487</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1043,124 +1073,124 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>2326917</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>1830265</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>4379246</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>198972</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1171,66 +1201,258 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>414981</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>500000</x:v>
+        <x:v>1830265</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:10">
+      <x:c r="A20" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H20" s="1">
+        <x:v>4379246</x:v>
+      </x:c>
+      <x:c r="I20" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J20" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:10">
+      <x:c r="A21" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H21" s="1">
+        <x:v>198972</x:v>
+      </x:c>
+      <x:c r="I21" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J21" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:10">
+      <x:c r="A22" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H22" s="1">
+        <x:v>414981</x:v>
+      </x:c>
+      <x:c r="I22" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10">
+      <x:c r="A23" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H23" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I23" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10">
+      <x:c r="A24" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H24" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I24" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10">
+      <x:c r="A25" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H25" s="1">
+        <x:v>38952</x:v>
+      </x:c>
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -88,6 +88,24 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6CA22208</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00936724</x:t>
   </x:si>
   <x:si>
@@ -145,9 +163,6 @@
     <x:t>48</x:t>
   </x:si>
   <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6NE02190</x:t>
   </x:si>
   <x:si>
@@ -160,12 +175,6 @@
     <x:t>NE</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00799031</x:t>
   </x:si>
   <x:si>
@@ -251,9 +260,6 @@
   </x:si>
   <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>H6NJ11310</x:t>
@@ -333,8 +339,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
-  <x:autoFilter ref="A1:J25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J26" totalsRowShown="0">
+  <x:autoFilter ref="A1:J26"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -639,7 +645,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J25"/>
+  <x:dimension ref="A1:J26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -800,13 +806,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>3985700</x:v>
+        <x:v>30683</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -817,28 +823,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>50710</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -849,48 +855,48 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>1426379</x:v>
+        <x:v>50710</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>14</x:v>
@@ -902,21 +908,21 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>149773</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>40</x:v>
@@ -928,45 +934,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1500000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>1870</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -977,28 +983,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>198972</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1009,60 +1015,60 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="G12" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H12" s="1">
-        <x:v>4968502</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>500346</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1079,10 +1085,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
@@ -1094,7 +1100,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>4383749</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1105,28 +1111,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>600000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1137,74 +1143,74 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>59748</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>374487</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>65</x:v>
@@ -1216,45 +1222,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>2326917</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>1830265</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1265,60 +1271,60 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1830265</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>198972</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1329,28 +1335,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>414981</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1361,42 +1367,42 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>500000</x:v>
+        <x:v>414981</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>80</x:v>
@@ -1408,50 +1414,82 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>350000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
+      <x:c r="H25" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
+      <x:c r="A26" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H25" s="1">
+      <x:c r="D26" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H26" s="1">
         <x:v>38952</x:v>
       </x:c>
-      <x:c r="I25" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J25" s="1" t="s">
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -218,6 +218,18 @@
   </x:si>
   <x:si>
     <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX35095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
   </x:si>
   <x:si>
     <x:t>H8NJ07223</x:t>
@@ -339,8 +351,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J26" totalsRowShown="0">
-  <x:autoFilter ref="A1:J26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J27" totalsRowShown="0">
+  <x:autoFilter ref="A1:J27"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -645,7 +657,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J26"/>
+  <x:dimension ref="A1:J27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1228,7 +1240,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>374487</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1239,10 +1251,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>68</x:v>
@@ -1254,19 +1266,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>2326917</x:v>
+        <x:v>43455</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
@@ -1277,22 +1289,22 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>1830265</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1303,10 +1315,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>74</x:v>
@@ -1318,33 +1330,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2618033</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
@@ -1353,10 +1365,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>198972</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1367,28 +1379,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>414981</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1399,97 +1411,129 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>500000</x:v>
+        <x:v>414981</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H26" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
+      <x:c r="A27" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H27" s="1">
         <x:v>38952</x:v>
       </x:c>
-      <x:c r="I26" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J26" s="1" t="s">
+      <x:c r="I27" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -94,6 +94,18 @@
     <x:t>EDW ACTION FUND</x:t>
   </x:si>
   <x:si>
+    <x:t>H6CA06276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6CA22208</x:t>
   </x:si>
   <x:si>
@@ -101,9 +113,6 @@
   </x:si>
   <x:si>
     <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
   </x:si>
   <x:si>
     <x:t>C00936724</x:t>
@@ -351,8 +360,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J27" totalsRowShown="0">
-  <x:autoFilter ref="A1:J27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0">
+  <x:autoFilter ref="A1:J28"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -657,7 +666,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J27"/>
+  <x:dimension ref="A1:J28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -824,7 +833,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>30683</x:v>
+        <x:v>15206</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -835,28 +844,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>3985700</x:v>
+        <x:v>61446</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -867,28 +876,28 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
+      <x:c r="C7" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>50710</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -899,48 +908,48 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>1426379</x:v>
+        <x:v>140153</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
@@ -952,53 +961,53 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>149773</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>1500000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>49</x:v>
@@ -1013,10 +1022,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1870</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1027,28 +1036,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>198972</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1059,60 +1068,60 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>4968502</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>500346</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1123,16 +1132,16 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
@@ -1144,7 +1153,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>4383749</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1155,28 +1164,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>600000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1187,74 +1196,74 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>59748</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>579319</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>68</x:v>
@@ -1266,13 +1275,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="H19" s="1">
-        <x:v>43455</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1283,60 +1292,60 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>2326917</x:v>
+        <x:v>43455</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>2618033</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1347,60 +1356,60 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
+      <x:c r="D22" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2618033</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>198972</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1411,28 +1420,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>414981</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1443,97 +1452,129 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>500000</x:v>
+        <x:v>443469</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>350000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H27" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I27" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:10">
+      <x:c r="A28" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H28" s="1">
         <x:v>38952</x:v>
       </x:c>
-      <x:c r="I27" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J27" s="1" t="s">
+      <x:c r="I28" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1313,7 +1313,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>43455</x:v>
+        <x:v>87010</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>2618033</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -184,48 +184,27 @@
     <x:t>NE</x:t>
   </x:si>
   <x:si>
+    <x:t>H6IL09194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00799031</x:t>
   </x:si>
   <x:si>
     <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
   </x:si>
   <x:si>
-    <x:t>H4IL07177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL09194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2NC06114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
+    <x:t>H6KY04171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
     <x:t>04</x:t>
   </x:si>
   <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL07339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6KY04171</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
     <x:t>KY</x:t>
   </x:si>
   <x:si>
@@ -281,15 +260,6 @@
   </x:si>
   <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NJ11310</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -360,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0">
-  <x:autoFilter ref="A1:J28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
+  <x:autoFilter ref="A1:J22"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -666,7 +636,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J28"/>
+  <x:dimension ref="A1:J22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -929,7 +899,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>140153</x:v>
+        <x:v>165658</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1100,28 +1070,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>4968502</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1132,10 +1102,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>60</x:v>
@@ -1147,13 +1117,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>500346</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1164,28 +1134,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>4383749</x:v>
+        <x:v>87010</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1196,60 +1166,60 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>600000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>59748</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1260,28 +1230,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>579319</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1292,28 +1262,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>87010</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1324,258 +1294,66 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>2326917</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>3576967</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:10">
-      <x:c r="A23" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H23" s="1">
-        <x:v>4379246</x:v>
-      </x:c>
-      <x:c r="I23" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J23" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:10">
-      <x:c r="A24" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H24" s="1">
-        <x:v>198972</x:v>
-      </x:c>
-      <x:c r="I24" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J24" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:10">
-      <x:c r="A25" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H25" s="1">
-        <x:v>443469</x:v>
-      </x:c>
-      <x:c r="I25" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J25" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:10">
-      <x:c r="A26" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H26" s="1">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="I26" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J26" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:10">
-      <x:c r="A27" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B27" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C27" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H27" s="1">
-        <x:v>350000</x:v>
-      </x:c>
-      <x:c r="I27" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J27" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:10">
-      <x:c r="A28" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H28" s="1">
-        <x:v>38952</x:v>
-      </x:c>
-      <x:c r="I28" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J28" s="1" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -190,6 +190,18 @@
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
+    <x:t>H6TX35103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00799031</x:t>
   </x:si>
   <x:si>
@@ -212,12 +224,6 @@
   </x:si>
   <x:si>
     <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
   </x:si>
   <x:si>
     <x:t>H8NJ07223</x:t>
@@ -330,8 +336,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
-  <x:autoFilter ref="A1:J22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
+  <x:autoFilter ref="A1:J23"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -636,7 +642,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J22"/>
+  <x:dimension ref="A1:J23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -803,7 +809,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>15206</x:v>
+        <x:v>30412</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -995,7 +1001,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1500000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1102,42 +1108,42 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>579319</x:v>
+        <x:v>10864</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>64</x:v>
@@ -1155,7 +1161,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>87010</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1166,10 +1172,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>68</x:v>
@@ -1181,27 +1187,27 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>2326917</x:v>
+        <x:v>119601</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>70</x:v>
@@ -1213,13 +1219,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>3576967</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1230,42 +1236,42 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>76</x:v>
@@ -1280,10 +1286,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>198972</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1294,10 +1300,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>78</x:v>
@@ -1309,13 +1315,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>499161</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1326,10 +1332,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>80</x:v>
@@ -1341,18 +1347,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H22" s="1">
+        <x:v>499161</x:v>
+      </x:c>
+      <x:c r="I22" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10">
+      <x:c r="A23" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H23" s="1">
         <x:v>500000</x:v>
       </x:c>
-      <x:c r="I22" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J22" s="1" t="s">
+      <x:c r="I23" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -905,7 +905,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>165658</x:v>
+        <x:v>209658</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -266,6 +266,15 @@
   </x:si>
   <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8CA11116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -336,8 +345,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
-  <x:autoFilter ref="A1:J23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
+  <x:autoFilter ref="A1:J24"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -642,7 +651,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J23"/>
+  <x:dimension ref="A1:J24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -809,7 +818,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>30412</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1129,7 +1138,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>10864</x:v>
+        <x:v>12864</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1392,6 +1401,38 @@
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10">
+      <x:c r="A24" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H24" s="1">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="I24" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -850,7 +850,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>61446</x:v>
+        <x:v>91433</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1202,7 +1202,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>119601</x:v>
+        <x:v>163056</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1138,7 +1138,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>12864</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1202,7 +1202,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>163056</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -157,6 +157,24 @@
     <x:t>J STREET ACTION FUND</x:t>
   </x:si>
   <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6MD05321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00710848</x:t>
   </x:si>
   <x:si>
@@ -200,12 +218,6 @@
   </x:si>
   <x:si>
     <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
   </x:si>
   <x:si>
     <x:t>H6KY04171</x:t>
@@ -345,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
-  <x:autoFilter ref="A1:J24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
+  <x:autoFilter ref="A1:J25"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -651,7 +663,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J24"/>
+  <x:dimension ref="A1:J25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1007,42 +1019,42 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1750000</x:v>
+        <x:v>51639</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>1870</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1053,28 +1065,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>198972</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1085,74 +1097,74 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>4383749</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>14264</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>64</x:v>
@@ -1170,13 +1182,13 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>579319</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
@@ -1196,13 +1208,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>163756</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1213,60 +1225,60 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>2326917</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>3576967</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1277,10 +1289,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>76</x:v>
@@ -1292,45 +1304,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>198972</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1341,28 +1353,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>499161</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1373,65 +1385,97 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>500000</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H24" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I24" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10">
+      <x:c r="A25" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H25" s="1">
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="I24" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J24" s="1" t="s">
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -926,7 +926,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>209658</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1054,7 +1054,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -862,7 +862,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>91433</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1022,7 +1022,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>51639</x:v>
+        <x:v>1238800</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1022,7 +1022,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1238800</x:v>
+        <x:v>1290439</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1022,7 +1022,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1290439</x:v>
+        <x:v>1415439</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1022,7 +1022,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1415439</x:v>
+        <x:v>1524553</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -151,133 +151,145 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6MD05321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8CA50098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NE02190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL09194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX35103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6KY04171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX35095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8NJ07223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2KY04121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8UT04053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL02355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NE02174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8CA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6CA22190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00815753</x:t>
   </x:si>
   <x:si>
     <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6MD05321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8CA50098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NE02190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL09194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35103</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6KY04171</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8NJ07223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2KY04121</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL02355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NE02174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8CA01109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA22190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
   <x:si>
     <x:t>H8CA11116</x:t>
@@ -975,22 +987,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>149773</x:v>
+        <x:v>1524553</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1001,60 +1013,60 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1524553</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>2000000</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1065,28 +1077,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>1870</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1097,42 +1109,42 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>198972</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>62</x:v>
@@ -1144,77 +1156,77 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>4383749</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>14264</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>579319</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1225,10 +1237,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>72</x:v>
@@ -1240,27 +1252,27 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>163756</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>74</x:v>
@@ -1272,13 +1284,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>2326917</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1289,10 +1301,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>76</x:v>
@@ -1304,39 +1316,39 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>3576967</x:v>
+        <x:v>181000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>16</x:v>
@@ -1359,19 +1371,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>198972</x:v>
@@ -1391,16 +1403,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>29</x:v>
@@ -1417,16 +1429,16 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
@@ -1449,22 +1461,22 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>29</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1002,7 +1002,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>1524553</x:v>
+        <x:v>2811685</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -272,6 +272,21 @@
   </x:si>
   <x:si>
     <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6MI00426</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
   </x:si>
   <x:si>
     <x:t>H8CA01109</x:t>
@@ -369,8 +384,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
-  <x:autoFilter ref="A1:J25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J26" totalsRowShown="0">
+  <x:autoFilter ref="A1:J26"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -675,7 +690,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J25"/>
+  <x:dimension ref="A1:J26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1397,10 +1412,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>86</x:v>
@@ -1409,16 +1424,16 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>499161</x:v>
+        <x:v>2464275</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1429,65 +1444,97 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>500000</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H25" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
+      <x:c r="A26" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H26" s="1">
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="I25" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J25" s="1" t="s">
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1017,7 +1017,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>2811685</x:v>
+        <x:v>2913324</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1209,7 +1209,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>579319</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1305,7 +1305,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>3576967</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1017,7 +1017,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>2913324</x:v>
+        <x:v>2926736</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1017,7 +1017,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>2926736</x:v>
+        <x:v>5434539</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1433,7 +1433,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>2464275</x:v>
+        <x:v>4905805</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1017,7 +1017,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>5434539</x:v>
+        <x:v>5734014</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1337,7 +1337,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>181000</x:v>
+        <x:v>186455</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1433,7 +1433,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>4905805</x:v>
+        <x:v>4923593</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1465,7 +1465,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>499161</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1337,7 +1337,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>186455</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -272,6 +272,15 @@
   </x:si>
   <x:si>
     <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NH01321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
   </x:si>
   <x:si>
     <x:t>S6MI00426</x:t>
@@ -384,8 +393,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J26" totalsRowShown="0">
-  <x:autoFilter ref="A1:J26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J27" totalsRowShown="0">
+  <x:autoFilter ref="A1:J27"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -690,7 +699,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J26"/>
+  <x:dimension ref="A1:J27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1412,10 +1421,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>86</x:v>
@@ -1424,16 +1433,16 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="H23" s="1">
-        <x:v>4923593</x:v>
+        <x:v>80291</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1444,28 +1453,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="F24" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>468360</x:v>
+        <x:v>7354888</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1476,65 +1485,97 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>500000</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H26" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
+      <x:c r="A27" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H27" s="1">
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="I26" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J26" s="1" t="s">
+      <x:c r="I27" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -184,94 +184,79 @@
     <x:t>48</x:t>
   </x:si>
   <x:si>
-    <x:t>H6NE02190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
+    <x:t>H6IL09194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX35103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6KY04171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX35095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8NJ07223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2KY04121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8UT04053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL02355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
   </x:si>
   <x:si>
     <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL09194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35103</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6KY04171</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8NJ07223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2KY04121</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8UT04053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL02355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NE02174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
   </x:si>
   <x:si>
     <x:t>H6NH01321</x:t>
@@ -393,8 +378,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J27" totalsRowShown="0">
-  <x:autoFilter ref="A1:J27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
+  <x:autoFilter ref="A1:J24"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -699,7 +684,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J27"/>
+  <x:dimension ref="A1:J24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1058,7 +1043,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>2000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1069,10 +1054,10 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>56</x:v>
@@ -1084,45 +1069,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>1870</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>198972</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1133,28 +1118,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>4383749</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1171,28 +1156,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>14264</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
@@ -1203,36 +1188,36 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>360170</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>70</x:v>
@@ -1250,21 +1235,21 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>163756</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>72</x:v>
@@ -1276,51 +1261,51 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>2326917</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>2335126</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
@@ -1331,22 +1316,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>195838</x:v>
+        <x:v>80291</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1357,28 +1342,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>4379246</x:v>
+        <x:v>7354888</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1389,28 +1374,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>198972</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1421,161 +1406,65 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>80291</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>7354888</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:10">
-      <x:c r="A25" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H25" s="1">
-        <x:v>468360</x:v>
-      </x:c>
-      <x:c r="I25" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J25" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:10">
-      <x:c r="A26" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H26" s="1">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="I26" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J26" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:10">
-      <x:c r="A27" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B27" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C27" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H27" s="1">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="I27" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J27" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1331,7 +1331,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>80291</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -184,6 +184,21 @@
     <x:t>48</x:t>
   </x:si>
   <x:si>
+    <x:t>S6MI00418</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
@@ -202,6 +217,12 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6KY04171</x:t>
   </x:si>
   <x:si>
@@ -220,6 +241,24 @@
     <x:t>GARCIA, JOHNNY</x:t>
   </x:si>
   <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2NY10308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
     <x:t>H8NJ07223</x:t>
   </x:si>
   <x:si>
@@ -272,15 +311,6 @@
   </x:si>
   <x:si>
     <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
   </x:si>
   <x:si>
     <x:t>H8CA01109</x:t>
@@ -378,8 +408,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
-  <x:autoFilter ref="A1:J24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0">
+  <x:autoFilter ref="A1:J28"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -684,7 +714,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J24"/>
+  <x:dimension ref="A1:J28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1054,10 +1084,10 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>56</x:v>
@@ -1066,112 +1096,112 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>4383749</x:v>
+        <x:v>2346358</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>14264</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>360170</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>163756</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1188,86 +1218,86 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>2326917</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>2335126</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>195838</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1278,66 +1308,66 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>130183</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1348,28 +1378,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>7354888</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
@@ -1380,22 +1410,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>468360</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1406,10 +1436,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>91</x:v>
@@ -1421,50 +1451,178 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>500000</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
+      <x:c r="H24" s="1">
+        <x:v>130183</x:v>
+      </x:c>
+      <x:c r="I24" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10">
+      <x:c r="A25" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G24" s="1" t="s">
+      <x:c r="D25" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H25" s="1">
+        <x:v>8437450</x:v>
+      </x:c>
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
+      <x:c r="A26" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H24" s="1">
+      <x:c r="H26" s="1">
+        <x:v>468360</x:v>
+      </x:c>
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
+      <x:c r="A27" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H27" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I27" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:10">
+      <x:c r="A28" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H28" s="1">
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="I24" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J24" s="1" t="s">
+      <x:c r="I28" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -283,6 +283,18 @@
     <x:t>UT</x:t>
   </x:si>
   <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6MI00392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00935049</x:t>
   </x:si>
   <x:si>
@@ -323,12 +335,6 @@
   </x:si>
   <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
   </x:si>
   <x:si>
     <x:t>H8CA11116</x:t>
@@ -408,8 +414,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0">
-  <x:autoFilter ref="A1:J28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
+  <x:autoFilter ref="A1:J29"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -714,7 +720,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J28"/>
+  <x:dimension ref="A1:J29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1448,16 +1454,16 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>4379246</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1468,28 +1474,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>130183</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1500,28 +1506,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>8437450</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1532,28 +1538,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>468360</x:v>
+        <x:v>8437450</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1564,42 +1570,42 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>500000</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>105</x:v>
@@ -1611,18 +1617,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H28" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I28" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10">
+      <x:c r="A29" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H29" s="1">
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="I28" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J28" s="1" t="s">
+      <x:c r="I29" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -127,6 +127,24 @@
     <x:t>BEAN, MELISSA LUBURICH</x:t>
   </x:si>
   <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4MO01134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
@@ -151,12 +169,6 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6MD05321</x:t>
   </x:si>
   <x:si>
@@ -275,9 +287,6 @@
   </x:si>
   <x:si>
     <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
   </x:si>
   <x:si>
     <x:t>UT</x:t>
@@ -414,8 +423,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
-  <x:autoFilter ref="A1:J29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J30" totalsRowShown="0">
+  <x:autoFilter ref="A1:J30"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -720,7 +729,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J29"/>
+  <x:dimension ref="A1:J30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -983,7 +992,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>253658</x:v>
+        <x:v>542439</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -994,124 +1003,124 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1426379</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>5734014</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="G11" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>1000000</x:v>
+        <x:v>5734014</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>2346358</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1122,124 +1131,124 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>4383749</x:v>
+        <x:v>2350379</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>14264</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>3515616</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>360170</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1250,10 +1259,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>73</x:v>
@@ -1265,13 +1274,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>163756</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1282,10 +1291,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>77</x:v>
@@ -1297,13 +1306,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>10000</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1314,10 +1323,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>81</x:v>
@@ -1329,45 +1338,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>2326917</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1378,28 +1387,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>2335126</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1416,54 +1425,54 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>195838</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="H23" s="1">
-        <x:v>50000</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1474,28 +1483,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
+      <x:c r="C24" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>4379246</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1506,10 +1515,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>98</x:v>
@@ -1521,13 +1530,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>130183</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1538,10 +1547,10 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>101</x:v>
@@ -1550,16 +1559,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>8437450</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1576,22 +1585,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>468360</x:v>
+        <x:v>8609875</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1602,65 +1611,97 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>500000</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H29" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I29" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
+      <x:c r="A30" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H30" s="1">
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="I29" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J29" s="1" t="s">
+      <x:c r="I30" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J30" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -344,15 +344,6 @@
   </x:si>
   <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8CA11116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -423,8 +414,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J30" totalsRowShown="0">
-  <x:autoFilter ref="A1:J30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
+  <x:autoFilter ref="A1:J29"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -729,7 +720,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J30"/>
+  <x:dimension ref="A1:J29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1673,38 +1664,6 @@
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:10">
-      <x:c r="A30" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H30" s="1">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="I30" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J30" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1591,7 +1591,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>8609875</x:v>
+        <x:v>9232574</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1143,7 +1143,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>2350379</x:v>
+        <x:v>5654811</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1559,7 +1559,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>130183</x:v>
+        <x:v>180941</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -179,6 +179,12 @@
   </x:si>
   <x:si>
     <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8MO01143</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
   </x:si>
   <x:si>
     <x:t>C00710848</x:t>
@@ -414,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
-  <x:autoFilter ref="A1:J29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J30" totalsRowShown="0">
+  <x:autoFilter ref="A1:J30"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -720,7 +726,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J29"/>
+  <x:dimension ref="A1:J30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -983,7 +989,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>542439</x:v>
+        <x:v>628944</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1090,28 +1096,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>1000000</x:v>
+        <x:v>510074</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1122,28 +1128,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>5654811</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1154,42 +1160,42 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>4383749</x:v>
+        <x:v>5709131</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>67</x:v>
@@ -1201,77 +1207,77 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>14264</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>3515616</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>360170</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1282,28 +1288,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="G18" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>163756</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1314,28 +1320,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>10000</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1346,42 +1352,42 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="G20" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>2326917</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>87</x:v>
@@ -1393,13 +1399,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1410,28 +1416,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>2335126</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1442,10 +1448,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>89</x:v>
@@ -1457,45 +1463,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>195838</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="H24" s="1">
-        <x:v>50000</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1506,28 +1512,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
+      <x:c r="D25" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>4379246</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1538,28 +1544,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>180941</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1570,28 +1576,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
+      <x:c r="E27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="H27" s="1">
-        <x:v>9232574</x:v>
+        <x:v>180941</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1602,10 +1608,10 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>106</x:v>
@@ -1614,16 +1620,16 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>468360</x:v>
+        <x:v>9262703</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1634,10 +1640,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>108</x:v>
@@ -1649,18 +1655,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H29" s="1">
+        <x:v>468360</x:v>
+      </x:c>
+      <x:c r="I29" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
+      <x:c r="A30" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H30" s="1">
         <x:v>500000</x:v>
       </x:c>
-      <x:c r="I29" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J29" s="1" t="s">
+      <x:c r="I30" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J30" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -420,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J30" totalsRowShown="0">
-  <x:autoFilter ref="A1:J30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0">
+  <x:autoFilter ref="A1:J28"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -726,7 +726,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J30"/>
+  <x:dimension ref="A1:J28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1085,7 +1085,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>5734014</x:v>
+        <x:v>4495214</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1288,28 +1288,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>360170</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1320,28 +1320,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>163756</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1352,60 +1352,60 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>10000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>2326917</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1416,92 +1416,92 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>3232621</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>2335126</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>195838</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1512,28 +1512,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>50000</x:v>
+        <x:v>227823</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1544,28 +1544,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>4379246</x:v>
+        <x:v>9262703</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1582,22 +1582,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>180941</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1608,97 +1608,33 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>9262703</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:10">
-      <x:c r="A29" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H29" s="1">
-        <x:v>468360</x:v>
-      </x:c>
-      <x:c r="I29" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J29" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:10">
-      <x:c r="A30" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H30" s="1">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="I30" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J30" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -420,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0">
-  <x:autoFilter ref="A1:J28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
+  <x:autoFilter ref="A1:J29"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -726,7 +726,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J28"/>
+  <x:dimension ref="A1:J29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1117,7 +1117,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>510074</x:v>
+        <x:v>1116191</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1181,7 +1181,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>5709131</x:v>
+        <x:v>9696759</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1544,10 +1544,10 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>106</x:v>
@@ -1565,7 +1565,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>9262703</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1576,28 +1576,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>468360</x:v>
+        <x:v>9772366</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1608,33 +1608,65 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H28" s="1">
+        <x:v>468360</x:v>
+      </x:c>
+      <x:c r="I28" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10">
+      <x:c r="A29" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H29" s="1">
         <x:v>500000</x:v>
       </x:c>
-      <x:c r="I28" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J28" s="1" t="s">
+      <x:c r="I29" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -420,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
-  <x:autoFilter ref="A1:J29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J30" totalsRowShown="0">
+  <x:autoFilter ref="A1:J30"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -726,7 +726,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J29"/>
+  <x:dimension ref="A1:J30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1117,7 +1117,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>1116191</x:v>
+        <x:v>1177753</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1181,7 +1181,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>9696759</x:v>
+        <x:v>9760810</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>227823</x:v>
+        <x:v>409773</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1576,10 +1576,10 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>106</x:v>
@@ -1597,7 +1597,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>9772366</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1608,28 +1608,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>468360</x:v>
+        <x:v>9888936</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1640,33 +1640,65 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H29" s="1">
+        <x:v>468360</x:v>
+      </x:c>
+      <x:c r="I29" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
+      <x:c r="A30" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H30" s="1">
         <x:v>500000</x:v>
       </x:c>
-      <x:c r="I29" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J29" s="1" t="s">
+      <x:c r="I30" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J30" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -88,33 +88,6 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA06276</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA22208</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00936724</x:t>
   </x:si>
   <x:si>
@@ -145,46 +118,154 @@
     <x:t>MO</x:t>
   </x:si>
   <x:si>
+    <x:t>H6IL09228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6MD05321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8MO01143</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6MI00418</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL09194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6KY04171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2NY10308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8NJ07223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2KY04121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
     <x:t>ARTICLE ONE PAC</x:t>
   </x:si>
   <x:si>
-    <x:t>H6NJ07201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL09228</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6MD05321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8MO01143</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
+    <x:t>H8UT04053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6MI00392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL02355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NH01321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
   </x:si>
   <x:si>
     <x:t>C00710848</x:t>
@@ -193,163 +274,10 @@
     <x:t>DMFI PAC</x:t>
   </x:si>
   <x:si>
-    <x:t>H8CA50098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6MI00418</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL09194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35103</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6KY04171</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2NY10308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8NJ07223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2KY04121</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8UT04053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6MI00392</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL02355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NH01321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6MI00426</x:t>
   </x:si>
   <x:si>
     <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8CA01109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA22190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -420,8 +348,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J30" totalsRowShown="0">
-  <x:autoFilter ref="A1:J30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
+  <x:autoFilter ref="A1:J22"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -726,7 +654,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J30"/>
+  <x:dimension ref="A1:J22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -887,13 +815,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>63297</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -904,10 +832,10 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>30</x:v>
@@ -922,10 +850,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>152762</x:v>
+        <x:v>628944</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -936,60 +864,60 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>3985700</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
+      <x:c r="G8" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H8" s="1">
-        <x:v>628944</x:v>
+        <x:v>4495214</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1000,60 +928,60 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>253658</x:v>
+        <x:v>1177753</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>1426379</x:v>
+        <x:v>9760810</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1064,28 +992,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>4495214</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1096,92 +1024,92 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>1177753</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>1000000</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>9760810</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1192,42 +1120,42 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>69</x:v>
@@ -1239,45 +1167,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>14264</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="C17" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="D17" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>3515616</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1288,28 +1216,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>163756</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1320,28 +1248,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="H19" s="1">
-        <x:v>10000</x:v>
+        <x:v>409773</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1352,354 +1280,98 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>2326917</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>3232621</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>195838</x:v>
+        <x:v>9888936</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:10">
-      <x:c r="A23" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H23" s="1">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="I23" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J23" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:10">
-      <x:c r="A24" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H24" s="1">
-        <x:v>4379246</x:v>
-      </x:c>
-      <x:c r="I24" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J24" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:10">
-      <x:c r="A25" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H25" s="1">
-        <x:v>409773</x:v>
-      </x:c>
-      <x:c r="I25" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J25" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:10">
-      <x:c r="A26" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H26" s="1">
-        <x:v>31115</x:v>
-      </x:c>
-      <x:c r="I26" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J26" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:10">
-      <x:c r="A27" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B27" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C27" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H27" s="1">
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="I27" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J27" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:10">
-      <x:c r="A28" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H28" s="1">
-        <x:v>9888936</x:v>
-      </x:c>
-      <x:c r="I28" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J28" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:10">
-      <x:c r="A29" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H29" s="1">
-        <x:v>468360</x:v>
-      </x:c>
-      <x:c r="I29" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J29" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:10">
-      <x:c r="A30" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H30" s="1">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="I30" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J30" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -949,7 +949,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1177753</x:v>
+        <x:v>1239979</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -981,7 +981,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>9760810</x:v>
+        <x:v>10036911</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -949,7 +949,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1239979</x:v>
+        <x:v>1901377</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -981,7 +981,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>10036911</x:v>
+        <x:v>14760156</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>409773</x:v>
+        <x:v>465686</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1365,7 +1365,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>9888936</x:v>
+        <x:v>10036699</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -853,7 +853,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>628944</x:v>
+        <x:v>654844</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -949,7 +949,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1901377</x:v>
+        <x:v>1927277</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -981,7 +981,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>14760156</x:v>
+        <x:v>14808128</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1365,7 +1365,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>10036699</x:v>
+        <x:v>10154402</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -949,7 +949,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1927277</x:v>
+        <x:v>1989796</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -981,7 +981,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>14808128</x:v>
+        <x:v>15095965</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -949,7 +949,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1989796</x:v>
+        <x:v>2427007</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -981,7 +981,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>15095965</x:v>
+        <x:v>20015158</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>465686</x:v>
+        <x:v>513656</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1365,7 +1365,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>10154402</x:v>
+        <x:v>10192938</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -853,7 +853,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>654844</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -949,7 +949,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>2427007</x:v>
+        <x:v>2457788</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -981,7 +981,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>20015158</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1365,7 +1365,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>10192938</x:v>
+        <x:v>10498737</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1269,7 +1269,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>513656</x:v>
+        <x:v>651086</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -181,103 +181,91 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>H8NJ07223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2KY04121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8UT04053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6MI00392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL02355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NH01321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6MI00426</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00684969</x:t>
   </x:si>
   <x:si>
     <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2NY10308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8NJ07223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2KY04121</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8UT04053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6MI00392</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL02355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NH01321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6MI00426</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -348,8 +336,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
-  <x:autoFilter ref="A1:J22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J21" totalsRowShown="0">
+  <x:autoFilter ref="A1:J21"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -654,7 +642,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J22"/>
+  <x:dimension ref="A1:J21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1056,60 +1044,60 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>10000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>2326917</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1120,60 +1108,60 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>3232621</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
+      <x:c r="C16" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>195838</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1184,28 +1172,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="D17" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>50000</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1216,28 +1204,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>4379246</x:v>
+        <x:v>651086</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1248,28 +1236,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>651086</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1280,16 +1268,16 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>44</x:v>
@@ -1301,7 +1289,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>31115</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1312,16 +1300,16 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>44</x:v>
@@ -1333,44 +1321,12 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>10000</x:v>
+        <x:v>10498737</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:10">
-      <x:c r="A22" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H22" s="1">
-        <x:v>10498737</x:v>
-      </x:c>
-      <x:c r="I22" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J22" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -181,6 +181,18 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>H6CA14163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H8NJ07223</x:t>
   </x:si>
   <x:si>
@@ -266,6 +278,15 @@
   </x:si>
   <x:si>
     <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0CA15213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -336,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J21" totalsRowShown="0">
-  <x:autoFilter ref="A1:J21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
+  <x:autoFilter ref="A1:J23"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -642,7 +663,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J21"/>
+  <x:dimension ref="A1:J23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1065,21 +1086,21 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>2326917</x:v>
+        <x:v>384198</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>59</x:v>
@@ -1091,13 +1112,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1108,10 +1129,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>63</x:v>
@@ -1123,45 +1144,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>195838</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
+      <x:c r="C16" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>50000</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1184,16 +1205,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>4379246</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1204,28 +1225,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>651086</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1236,28 +1257,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H19" s="1">
-        <x:v>31115</x:v>
+        <x:v>706754</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1274,10 +1295,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>44</x:v>
@@ -1289,7 +1310,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>10000</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1300,16 +1321,16 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>44</x:v>
@@ -1321,13 +1342,77 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>10498737</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:10">
+      <x:c r="A22" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H22" s="1">
+        <x:v>10498737</x:v>
+      </x:c>
+      <x:c r="I22" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10">
+      <x:c r="A23" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H23" s="1">
+        <x:v>818769</x:v>
+      </x:c>
+      <x:c r="I23" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1278,7 +1278,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>706754</x:v>
+        <x:v>766293</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1278,7 +1278,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>766293</x:v>
+        <x:v>825832</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1086,7 +1086,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>384198</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1406,7 +1406,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>818769</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -357,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
-  <x:autoFilter ref="A1:J23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
+  <x:autoFilter ref="A1:J24"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -663,7 +663,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J23"/>
+  <x:dimension ref="A1:J24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1385,10 +1385,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>88</x:v>
@@ -1406,12 +1406,44 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H23" s="1">
+        <x:v>108000</x:v>
+      </x:c>
+      <x:c r="I23" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10">
+      <x:c r="A24" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H24" s="1">
         <x:v>1642139</x:v>
       </x:c>
-      <x:c r="I23" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J23" s="1" t="s">
+      <x:c r="I24" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -124,18 +124,6 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
-    <x:t>H6MD05321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
     <x:t>H8MO01143</x:t>
   </x:si>
   <x:si>
@@ -211,46 +199,52 @@
     <x:t>MASSIE, THOMAS H.</x:t>
   </x:si>
   <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6MI00392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL02355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6AK00276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
     <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8UT04053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6MI00392</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL02355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
   </x:si>
   <x:si>
     <x:t>H6NH01321</x:t>
@@ -357,8 +351,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
-  <x:autoFilter ref="A1:J24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
+  <x:autoFilter ref="A1:J23"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -663,7 +657,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J24"/>
+  <x:dimension ref="A1:J23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -920,19 +914,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>4495214</x:v>
+        <x:v>2457788</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
@@ -943,22 +937,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="F9" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>2457788</x:v>
+        <x:v>17793547</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -969,42 +963,42 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>20139905</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>47</x:v>
@@ -1016,13 +1010,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1033,10 +1027,10 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>51</x:v>
@@ -1054,7 +1048,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>3515616</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1086,21 +1080,21 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>825294</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>59</x:v>
@@ -1112,13 +1106,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>2326917</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1129,10 +1123,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>63</x:v>
@@ -1141,22 +1135,22 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>3232621</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
@@ -1176,13 +1170,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>195838</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1205,16 +1199,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>50000</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1225,28 +1219,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>4379246</x:v>
+        <x:v>803627</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1257,28 +1251,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>825832</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1289,28 +1283,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>31115</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1321,28 +1315,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>10000</x:v>
+        <x:v>2061287</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1353,28 +1347,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>10498737</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1385,65 +1379,33 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>108000</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:10">
-      <x:c r="A24" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H24" s="1">
-        <x:v>1642139</x:v>
-      </x:c>
-      <x:c r="I24" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J24" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1240,7 +1240,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>803627</x:v>
+        <x:v>859295</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1240,7 +1240,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>859295</x:v>
+        <x:v>922241</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -266,12 +266,6 @@
   </x:si>
   <x:si>
     <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
   </x:si>
   <x:si>
     <x:t>H0CA15213</x:t>
@@ -351,8 +345,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
-  <x:autoFilter ref="A1:J23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
+  <x:autoFilter ref="A1:J22"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -657,7 +651,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J23"/>
+  <x:dimension ref="A1:J22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1283,10 +1277,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>82</x:v>
@@ -1304,7 +1298,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>10000</x:v>
+        <x:v>2061287</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1315,28 +1309,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>2061287</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1347,65 +1341,33 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>108000</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:10">
-      <x:c r="A23" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H23" s="1">
-        <x:v>1642139</x:v>
-      </x:c>
-      <x:c r="I23" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J23" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1234,7 +1234,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>922241</x:v>
+        <x:v>978007</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1234,7 +1234,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>978007</x:v>
+        <x:v>1134483</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1234,7 +1234,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>1134483</x:v>
+        <x:v>1137283</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
